--- a/repository_snapshot_portfolio_value_optie_call_put_detailed.xlsx
+++ b/repository_snapshot_portfolio_value_optie_call_put_detailed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python_coding\portefeuille_viewer\portefeuille_viewer_experiment_0.13\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71149643-675C-4DD2-A526-D45CE582632C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC71ACB-13B6-470D-AB1B-CEEB5E8131CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="-110" windowWidth="37130" windowHeight="21820" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1380" yWindow="-110" windowWidth="37130" windowHeight="21820" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Details1" sheetId="3" r:id="rId1"/>
@@ -6111,7 +6111,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:R100"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -6128,8 +6127,8 @@
     <col min="11" max="11" width="10.36328125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.1796875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.6328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="15" max="15" width="23.26953125" customWidth="1"/>
     <col min="16" max="16" width="5" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="18.1796875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="10.453125" bestFit="1" customWidth="1"/>
@@ -6191,7 +6190,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -6241,7 +6240,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -6291,7 +6290,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -6341,7 +6340,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -6391,7 +6390,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -6441,7 +6440,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -6491,7 +6490,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -6641,7 +6640,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -6691,7 +6690,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -6741,7 +6740,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -6791,7 +6790,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -6841,7 +6840,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -6891,7 +6890,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -6941,7 +6940,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -7091,7 +7090,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -7141,7 +7140,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -7191,7 +7190,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -7241,7 +7240,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>29</v>
       </c>
@@ -7341,7 +7340,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -7391,7 +7390,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -7441,7 +7440,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>24</v>
       </c>
@@ -7491,7 +7490,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -7591,7 +7590,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -7641,7 +7640,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="31" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -7691,7 +7690,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>24</v>
       </c>
@@ -7741,7 +7740,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>24</v>
       </c>
@@ -7791,7 +7790,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>29</v>
       </c>
@@ -7841,7 +7840,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="35" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -7891,7 +7890,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="36" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -7941,7 +7940,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>29</v>
       </c>
@@ -7991,7 +7990,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="38" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -8091,7 +8090,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="40" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>29</v>
       </c>
@@ -8141,7 +8140,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="41" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -8241,7 +8240,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>24</v>
       </c>
@@ -8341,7 +8340,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="45" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -8391,7 +8390,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="46" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>29</v>
       </c>
@@ -8441,7 +8440,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="47" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -8491,7 +8490,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="48" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>29</v>
       </c>
@@ -8541,7 +8540,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="49" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>24</v>
       </c>
@@ -8591,7 +8590,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="50" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>29</v>
       </c>
@@ -8641,7 +8640,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="51" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>29</v>
       </c>
@@ -8691,7 +8690,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="52" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>24</v>
       </c>
@@ -8741,7 +8740,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="53" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>29</v>
       </c>
@@ -8841,7 +8840,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="55" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -8891,7 +8890,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>29</v>
       </c>
@@ -8941,7 +8940,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="57" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>29</v>
       </c>
@@ -8991,7 +8990,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="58" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>29</v>
       </c>
@@ -9041,7 +9040,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="59" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -9091,7 +9090,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="60" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>29</v>
       </c>
@@ -9141,7 +9140,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="61" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>29</v>
       </c>
@@ -9191,7 +9190,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="62" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>24</v>
       </c>
@@ -9241,7 +9240,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>29</v>
       </c>
@@ -9291,7 +9290,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="64" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -9341,7 +9340,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="65" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>29</v>
       </c>
@@ -9391,7 +9390,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="66" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>24</v>
       </c>
@@ -9441,7 +9440,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="67" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>24</v>
       </c>
@@ -9491,7 +9490,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="68" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>24</v>
       </c>
@@ -9541,7 +9540,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="69" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>24</v>
       </c>
@@ -9591,7 +9590,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="70" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>24</v>
       </c>
@@ -9641,7 +9640,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="71" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>29</v>
       </c>
@@ -9691,7 +9690,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="72" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>29</v>
       </c>
@@ -9741,7 +9740,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="73" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -9791,7 +9790,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="74" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>29</v>
       </c>
@@ -9841,7 +9840,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="75" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>29</v>
       </c>
@@ -9891,7 +9890,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="76" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>24</v>
       </c>
@@ -9941,7 +9940,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="77" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>29</v>
       </c>
@@ -9991,7 +9990,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="78" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>18</v>
       </c>
@@ -10041,7 +10040,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="79" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>29</v>
       </c>
@@ -10091,7 +10090,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="80" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>24</v>
       </c>
@@ -10141,7 +10140,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="81" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>18</v>
       </c>
@@ -10191,7 +10190,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="82" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>29</v>
       </c>
@@ -10241,7 +10240,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="83" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>29</v>
       </c>
@@ -10291,7 +10290,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="84" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>29</v>
       </c>
@@ -10341,7 +10340,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="85" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>29</v>
       </c>
@@ -10391,7 +10390,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="86" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>18</v>
       </c>
@@ -10441,7 +10440,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="87" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>18</v>
       </c>
@@ -10491,7 +10490,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="88" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>18</v>
       </c>
@@ -10541,7 +10540,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="89" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>18</v>
       </c>
@@ -10591,7 +10590,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="90" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>29</v>
       </c>
@@ -10641,7 +10640,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="91" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>24</v>
       </c>
@@ -10691,7 +10690,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="92" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>29</v>
       </c>
@@ -10741,7 +10740,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="93" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>18</v>
       </c>
@@ -10791,7 +10790,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="94" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>24</v>
       </c>
@@ -10841,7 +10840,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="95" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>29</v>
       </c>
@@ -10891,7 +10890,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="96" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>24</v>
       </c>
@@ -10941,7 +10940,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="97" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>29</v>
       </c>
@@ -10991,7 +10990,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="98" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>29</v>
       </c>
@@ -11041,7 +11040,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="99" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -11091,7 +11090,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="100" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>24</v>
       </c>
@@ -11142,13 +11141,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R100" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="16">
-      <filters>
-        <filter val="Inf Tech"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:R100" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>